--- a/2026_spring/sem_1_intro/sessions_1_excel.xlsx
+++ b/2026_spring/sem_1_intro/sessions_1_excel.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>session_start</t>
+          <t>session_start_dttm</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
